--- a/artfynd/A 20705-2024 artfynd.xlsx
+++ b/artfynd/A 20705-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120311964</v>
+        <v>120311997</v>
       </c>
       <c r="B2" t="n">
-        <v>90546</v>
+        <v>91335</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4660</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562942</v>
+        <v>562921</v>
       </c>
       <c r="R2" t="n">
-        <v>6631741</v>
+        <v>6631742</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,12 +776,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blockrik ung blandskog</t>
+          <t>Ung blandskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Asp, högstubbe</t>
+          <t>Aspstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120311997</v>
+        <v>120311964</v>
       </c>
       <c r="B3" t="n">
-        <v>91317</v>
+        <v>90564</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +811,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562921</v>
+        <v>562942</v>
       </c>
       <c r="R3" t="n">
-        <v>6631742</v>
+        <v>6631741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,12 +892,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Ung blandskog</t>
+          <t>Blockrik ung blandskog</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Aspstubbe</t>
+          <t>Asp, högstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 20705-2024 artfynd.xlsx
+++ b/artfynd/A 20705-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120311997</v>
+        <v>120311964</v>
       </c>
       <c r="B2" t="n">
-        <v>91335</v>
+        <v>90564</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>4660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562921</v>
+        <v>562942</v>
       </c>
       <c r="R2" t="n">
-        <v>6631742</v>
+        <v>6631741</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,12 +768,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Ung blandskog</t>
+          <t>Blockrik ung blandskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Aspstubbe</t>
+          <t>Asp, högstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120311964</v>
+        <v>120311997</v>
       </c>
       <c r="B3" t="n">
-        <v>90564</v>
+        <v>91335</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,29 +803,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4660</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562942</v>
+        <v>562921</v>
       </c>
       <c r="R3" t="n">
-        <v>6631741</v>
+        <v>6631742</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,12 +892,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blockrik ung blandskog</t>
+          <t>Ung blandskog</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Asp, högstubbe</t>
+          <t>Aspstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 20705-2024 artfynd.xlsx
+++ b/artfynd/A 20705-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120311964</v>
+        <v>120311997</v>
       </c>
       <c r="B2" t="n">
-        <v>90564</v>
+        <v>91335</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4660</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562942</v>
+        <v>562921</v>
       </c>
       <c r="R2" t="n">
-        <v>6631741</v>
+        <v>6631742</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,12 +776,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blockrik ung blandskog</t>
+          <t>Ung blandskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Asp, högstubbe</t>
+          <t>Aspstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120311997</v>
+        <v>120311964</v>
       </c>
       <c r="B3" t="n">
-        <v>91335</v>
+        <v>90564</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +811,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562921</v>
+        <v>562942</v>
       </c>
       <c r="R3" t="n">
-        <v>6631742</v>
+        <v>6631741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,12 +892,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Ung blandskog</t>
+          <t>Blockrik ung blandskog</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Aspstubbe</t>
+          <t>Asp, högstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
